--- a/app/download_dir/system_files/носки_по каждому размеру.xlsx
+++ b/app/download_dir/system_files/носки_по каждому размеру.xlsx
@@ -277,7 +277,7 @@
     <t xml:space="preserve">БЕЖЕВЫЙ/СИНИЙ</t>
   </si>
   <si>
-    <t xml:space="preserve">Детск.</t>
+    <t xml:space="preserve">Без указания пола</t>
   </si>
   <si>
     <t xml:space="preserve">АЗЕРБАЙДЖАН</t>
@@ -2862,7 +2862,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AMJ1048576"/>
-  <sheetFormatPr defaultColWidth="12.40625" defaultRowHeight="12" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.42578125" defaultRowHeight="12" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.82"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="72.34"/>
@@ -15747,7 +15747,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F246"/>
-  <sheetFormatPr defaultColWidth="12.40625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.42578125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="37.18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24.58"/>
@@ -17418,7 +17418,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="C2:AD111"/>
-  <sheetFormatPr defaultColWidth="11.859375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="19.78"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="17.16"/>
@@ -18021,7 +18021,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:A1246"/>
-  <sheetFormatPr defaultColWidth="245.95703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="246.2265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1024" style="1" width="11.38"/>
   </cols>
